--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202607/Category_P&L_20260730.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202607/Category_P&L_20260730.xlsx
@@ -44917,7 +44917,7 @@
         <v>46233</v>
       </c>
       <c r="B1172">
-        <v>85859219.67</v>
+        <v>87859219.67</v>
       </c>
       <c r="C1172">
         <v>2560679.54</v>
